--- a/data/nzd0526/nzd0526.xlsx
+++ b/data/nzd0526/nzd0526.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S429"/>
+  <dimension ref="A1:S432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27425,6 +27425,195 @@
         <v>311.84</v>
       </c>
       <c r="S429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>326.44</v>
+      </c>
+      <c r="C430" t="n">
+        <v>320.35</v>
+      </c>
+      <c r="D430" t="n">
+        <v>318.01</v>
+      </c>
+      <c r="E430" t="n">
+        <v>317.51</v>
+      </c>
+      <c r="F430" t="n">
+        <v>319.2</v>
+      </c>
+      <c r="G430" t="n">
+        <v>326.29</v>
+      </c>
+      <c r="H430" t="n">
+        <v>327.47</v>
+      </c>
+      <c r="I430" t="n">
+        <v>325.79</v>
+      </c>
+      <c r="J430" t="n">
+        <v>323.29</v>
+      </c>
+      <c r="K430" t="n">
+        <v>311.01</v>
+      </c>
+      <c r="L430" t="n">
+        <v>309.8</v>
+      </c>
+      <c r="M430" t="n">
+        <v>313.42</v>
+      </c>
+      <c r="N430" t="n">
+        <v>327.99</v>
+      </c>
+      <c r="O430" t="n">
+        <v>321.71</v>
+      </c>
+      <c r="P430" t="n">
+        <v>310.65</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>302.38</v>
+      </c>
+      <c r="R430" t="n">
+        <v>308.24</v>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>327.58</v>
+      </c>
+      <c r="C431" t="n">
+        <v>317.66</v>
+      </c>
+      <c r="D431" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="E431" t="n">
+        <v>314.87</v>
+      </c>
+      <c r="F431" t="n">
+        <v>316.46</v>
+      </c>
+      <c r="G431" t="n">
+        <v>323.15</v>
+      </c>
+      <c r="H431" t="n">
+        <v>324.26</v>
+      </c>
+      <c r="I431" t="n">
+        <v>321.74</v>
+      </c>
+      <c r="J431" t="n">
+        <v>317.92</v>
+      </c>
+      <c r="K431" t="n">
+        <v>307.57</v>
+      </c>
+      <c r="L431" t="n">
+        <v>306.37</v>
+      </c>
+      <c r="M431" t="n">
+        <v>310.05</v>
+      </c>
+      <c r="N431" t="n">
+        <v>322.23</v>
+      </c>
+      <c r="O431" t="n">
+        <v>318.55</v>
+      </c>
+      <c r="P431" t="n">
+        <v>307.44</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>299.51</v>
+      </c>
+      <c r="R431" t="n">
+        <v>305.7</v>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>326.06</v>
+      </c>
+      <c r="C432" t="n">
+        <v>316.02</v>
+      </c>
+      <c r="D432" t="n">
+        <v>314.17</v>
+      </c>
+      <c r="E432" t="n">
+        <v>313.96</v>
+      </c>
+      <c r="F432" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="G432" t="n">
+        <v>322.03</v>
+      </c>
+      <c r="H432" t="n">
+        <v>322.92</v>
+      </c>
+      <c r="I432" t="n">
+        <v>319.53</v>
+      </c>
+      <c r="J432" t="n">
+        <v>316.31</v>
+      </c>
+      <c r="K432" t="n">
+        <v>306.22</v>
+      </c>
+      <c r="L432" t="n">
+        <v>304.35</v>
+      </c>
+      <c r="M432" t="n">
+        <v>308.05</v>
+      </c>
+      <c r="N432" t="n">
+        <v>317.01</v>
+      </c>
+      <c r="O432" t="n">
+        <v>316.4</v>
+      </c>
+      <c r="P432" t="n">
+        <v>305.62</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>297.7</v>
+      </c>
+      <c r="R432" t="n">
+        <v>303.87</v>
+      </c>
+      <c r="S432" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27441,7 +27630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B441"/>
+  <dimension ref="A1:B445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31854,6 +32043,46 @@
       </c>
       <c r="B441" t="n">
         <v>-1.06</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -32022,28 +32251,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.136863117471833</v>
+        <v>4.030999425159676</v>
       </c>
       <c r="J2" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K2" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L2" t="n">
-        <v>0.536678929324663</v>
+        <v>0.5158025585940375</v>
       </c>
       <c r="M2" t="n">
-        <v>24.24025180728493</v>
+        <v>24.62010386739638</v>
       </c>
       <c r="N2" t="n">
-        <v>850.1980982087651</v>
+        <v>885.4296643030465</v>
       </c>
       <c r="O2" t="n">
-        <v>29.15815663255764</v>
+        <v>29.75617018877004</v>
       </c>
       <c r="P2" t="n">
-        <v>293.2125694393375</v>
+        <v>294.316194372084</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32100,28 +32329,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.390553277044086</v>
+        <v>4.276773364571302</v>
       </c>
       <c r="J3" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K3" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5957812401047775</v>
+        <v>0.5718784666547765</v>
       </c>
       <c r="M3" t="n">
-        <v>22.71722084134601</v>
+        <v>23.15456150417573</v>
       </c>
       <c r="N3" t="n">
-        <v>747.8514544140158</v>
+        <v>789.8015260165615</v>
       </c>
       <c r="O3" t="n">
-        <v>27.34687284524532</v>
+        <v>28.10340772960748</v>
       </c>
       <c r="P3" t="n">
-        <v>282.9953714592127</v>
+        <v>284.1886573350318</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32178,28 +32407,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.121911624239377</v>
+        <v>4.013265874946295</v>
       </c>
       <c r="J4" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K4" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5865067833374014</v>
+        <v>0.562254591107249</v>
       </c>
       <c r="M4" t="n">
-        <v>21.6810652070461</v>
+        <v>22.09816877985745</v>
       </c>
       <c r="N4" t="n">
-        <v>690.2537059260468</v>
+        <v>728.8961056903653</v>
       </c>
       <c r="O4" t="n">
-        <v>26.27267983906565</v>
+        <v>26.998075962749</v>
       </c>
       <c r="P4" t="n">
-        <v>284.8545733621672</v>
+        <v>285.9871480788345</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32256,28 +32485,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.124612078578309</v>
+        <v>4.015370473854227</v>
       </c>
       <c r="J5" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K5" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5889820590762547</v>
+        <v>0.564410181546783</v>
       </c>
       <c r="M5" t="n">
-        <v>21.37900016948584</v>
+        <v>21.77486087323249</v>
       </c>
       <c r="N5" t="n">
-        <v>684.1336883453791</v>
+        <v>723.2947264231965</v>
       </c>
       <c r="O5" t="n">
-        <v>26.15594938719256</v>
+        <v>26.89413925789774</v>
       </c>
       <c r="P5" t="n">
-        <v>284.7763011177595</v>
+        <v>285.9150856979566</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32334,28 +32563,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.432940571432844</v>
+        <v>4.319104325117025</v>
       </c>
       <c r="J6" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K6" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6262448348763185</v>
+        <v>0.6013535976873292</v>
       </c>
       <c r="M6" t="n">
-        <v>21.00016660148315</v>
+        <v>21.43746302207088</v>
       </c>
       <c r="N6" t="n">
-        <v>675.8384705649087</v>
+        <v>718.8305065377768</v>
       </c>
       <c r="O6" t="n">
-        <v>25.99689347912378</v>
+        <v>26.81101464953866</v>
       </c>
       <c r="P6" t="n">
-        <v>281.4806018271262</v>
+        <v>282.6672828263303</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32412,28 +32641,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.183208120783279</v>
+        <v>4.074098775176073</v>
       </c>
       <c r="J7" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K7" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6235319943404654</v>
+        <v>0.5980799756803593</v>
       </c>
       <c r="M7" t="n">
-        <v>20.03557700798144</v>
+        <v>20.41217881807666</v>
       </c>
       <c r="N7" t="n">
-        <v>607.9930223453084</v>
+        <v>647.4900329644024</v>
       </c>
       <c r="O7" t="n">
-        <v>24.65751452083742</v>
+        <v>25.44582545260425</v>
       </c>
       <c r="P7" t="n">
-        <v>291.4719475607338</v>
+        <v>292.6094371318565</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32490,28 +32719,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.38935346778169</v>
+        <v>4.279183435648376</v>
       </c>
       <c r="J8" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K8" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6376234250012971</v>
+        <v>0.6132373172035959</v>
       </c>
       <c r="M8" t="n">
-        <v>20.4375081500993</v>
+        <v>20.81712446607542</v>
       </c>
       <c r="N8" t="n">
-        <v>632.6309406816018</v>
+        <v>673.0460133017594</v>
       </c>
       <c r="O8" t="n">
-        <v>25.15215578596797</v>
+        <v>25.94313036820652</v>
       </c>
       <c r="P8" t="n">
-        <v>287.8103450812759</v>
+        <v>288.9574898849337</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32568,28 +32797,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.482411605314788</v>
+        <v>4.370759324613596</v>
       </c>
       <c r="J9" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K9" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6460269247084522</v>
+        <v>0.6216183252457748</v>
       </c>
       <c r="M9" t="n">
-        <v>20.32795940947952</v>
+        <v>20.74317687279886</v>
       </c>
       <c r="N9" t="n">
-        <v>636.0577430889634</v>
+        <v>677.6836864607577</v>
       </c>
       <c r="O9" t="n">
-        <v>25.22018523105973</v>
+        <v>26.03235844983619</v>
       </c>
       <c r="P9" t="n">
-        <v>283.8637794448675</v>
+        <v>285.0263688023458</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32646,28 +32875,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.357361155775983</v>
+        <v>4.250397125021156</v>
       </c>
       <c r="J10" t="n">
+        <v>431</v>
+      </c>
+      <c r="K10" t="n">
         <v>428</v>
       </c>
-      <c r="K10" t="n">
-        <v>425</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.6073642961237122</v>
+        <v>0.5851859857539687</v>
       </c>
       <c r="M10" t="n">
-        <v>21.58260499016482</v>
+        <v>21.95959149211571</v>
       </c>
       <c r="N10" t="n">
-        <v>703.8941162147792</v>
+        <v>740.8111314635746</v>
       </c>
       <c r="O10" t="n">
-        <v>26.5310029251587</v>
+        <v>27.21784582702266</v>
       </c>
       <c r="P10" t="n">
-        <v>280.0912476930704</v>
+        <v>281.2112193137169</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32724,28 +32953,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.042798211249337</v>
+        <v>3.939862260153937</v>
       </c>
       <c r="J11" t="n">
+        <v>431</v>
+      </c>
+      <c r="K11" t="n">
         <v>428</v>
       </c>
-      <c r="K11" t="n">
-        <v>425</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.6018933780908902</v>
+        <v>0.5784658283635826</v>
       </c>
       <c r="M11" t="n">
-        <v>20.38677693410305</v>
+        <v>20.71492996834545</v>
       </c>
       <c r="N11" t="n">
-        <v>619.9599792860605</v>
+        <v>654.3440127649852</v>
       </c>
       <c r="O11" t="n">
-        <v>24.89899554773366</v>
+        <v>25.58014880263571</v>
       </c>
       <c r="P11" t="n">
-        <v>274.7033431629406</v>
+        <v>275.7811247174223</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32802,28 +33031,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.17826847708294</v>
+        <v>4.076790597162439</v>
       </c>
       <c r="J12" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K12" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6352034637107677</v>
+        <v>0.612353765325118</v>
       </c>
       <c r="M12" t="n">
-        <v>19.39630498562958</v>
+        <v>19.75291570049047</v>
       </c>
       <c r="N12" t="n">
-        <v>576.0767636381908</v>
+        <v>609.7833976471767</v>
       </c>
       <c r="O12" t="n">
-        <v>24.00159918918301</v>
+        <v>24.69379269466674</v>
       </c>
       <c r="P12" t="n">
-        <v>268.5852909393123</v>
+        <v>269.6472696848558</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32880,28 +33109,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>3.974561463628062</v>
+        <v>3.874104726184711</v>
       </c>
       <c r="J13" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K13" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6174794023888717</v>
+        <v>0.5936260509284818</v>
       </c>
       <c r="M13" t="n">
-        <v>19.37131150226304</v>
+        <v>19.69170298105097</v>
       </c>
       <c r="N13" t="n">
-        <v>564.278115707455</v>
+        <v>597.5396237219653</v>
       </c>
       <c r="O13" t="n">
-        <v>23.75453884434415</v>
+        <v>24.44462361587851</v>
       </c>
       <c r="P13" t="n">
-        <v>277.1347895048564</v>
+        <v>278.1848455136912</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32958,28 +33187,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3.809786341950886</v>
+        <v>3.723364946174508</v>
       </c>
       <c r="J14" t="n">
+        <v>431</v>
+      </c>
+      <c r="K14" t="n">
         <v>428</v>
       </c>
-      <c r="K14" t="n">
-        <v>425</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.6061978109393111</v>
+        <v>0.5868869704960433</v>
       </c>
       <c r="M14" t="n">
-        <v>18.86489579739046</v>
+        <v>19.16305842913541</v>
       </c>
       <c r="N14" t="n">
-        <v>543.8426815218962</v>
+        <v>567.7205796168391</v>
       </c>
       <c r="O14" t="n">
-        <v>23.32043484847348</v>
+        <v>23.8268877450841</v>
       </c>
       <c r="P14" t="n">
-        <v>283.3584442347923</v>
+        <v>284.2604438010642</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33036,28 +33265,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>2.961329930579782</v>
+        <v>2.876523549431252</v>
       </c>
       <c r="J15" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K15" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5326242423695238</v>
+        <v>0.5074523485708524</v>
       </c>
       <c r="M15" t="n">
-        <v>16.91043617280252</v>
+        <v>17.19789617098779</v>
       </c>
       <c r="N15" t="n">
-        <v>443.0004502094503</v>
+        <v>466.3803549485443</v>
       </c>
       <c r="O15" t="n">
-        <v>21.04757587489472</v>
+        <v>21.59584114936356</v>
       </c>
       <c r="P15" t="n">
-        <v>301.50695131881</v>
+        <v>302.3916827173972</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33114,28 +33343,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.790117736077412</v>
+        <v>2.705770902662558</v>
       </c>
       <c r="J16" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K16" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4817910104459733</v>
+        <v>0.4571447501132575</v>
       </c>
       <c r="M16" t="n">
-        <v>17.668517726155</v>
+        <v>17.9898995608017</v>
       </c>
       <c r="N16" t="n">
-        <v>482.0328460973176</v>
+        <v>504.8516093082442</v>
       </c>
       <c r="O16" t="n">
-        <v>21.95524643672481</v>
+        <v>22.46890316210928</v>
       </c>
       <c r="P16" t="n">
-        <v>294.7921578124371</v>
+        <v>295.6720936584995</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33192,28 +33421,28 @@
         <v>0.1976</v>
       </c>
       <c r="I17" t="n">
-        <v>2.547703942831717</v>
+        <v>2.466242153672035</v>
       </c>
       <c r="J17" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K17" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4282893596134391</v>
+        <v>0.4046134987745846</v>
       </c>
       <c r="M17" t="n">
-        <v>18.04652409360373</v>
+        <v>18.3755858278473</v>
       </c>
       <c r="N17" t="n">
-        <v>498.7951605812489</v>
+        <v>519.7343783022806</v>
       </c>
       <c r="O17" t="n">
-        <v>22.33372249718458</v>
+        <v>22.79768361703181</v>
       </c>
       <c r="P17" t="n">
-        <v>291.1549846429754</v>
+        <v>292.0048213000433</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33270,28 +33499,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2.116326250908567</v>
+        <v>2.046105370370852</v>
       </c>
       <c r="J18" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K18" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3807973014385828</v>
+        <v>0.3587841221756822</v>
       </c>
       <c r="M18" t="n">
-        <v>16.51845122262718</v>
+        <v>16.78508979809314</v>
       </c>
       <c r="N18" t="n">
-        <v>419.2658974434418</v>
+        <v>434.4886522118655</v>
       </c>
       <c r="O18" t="n">
-        <v>20.47598343043483</v>
+        <v>20.84439138501927</v>
       </c>
       <c r="P18" t="n">
-        <v>300.5746157888324</v>
+        <v>301.3071854306191</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33329,7 +33558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S429"/>
+  <dimension ref="A1:S432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74821,6 +75050,297 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-46.29881010111074,169.92335468664172</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-46.29901649113921,169.92250608843847</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-46.299253938365815,169.9216764575365</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-46.29950662378208,169.92085613303695</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-46.29977744633506,169.92004688473844</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-46.300093947659256,169.9192623559284</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-46.30038332943842,169.91846192257788</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-46.300665647500885,169.9176599319488</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>-46.30094062276259,169.91685493995735</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-46.3011349120796,169.91599855841068</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-46.30139490847767,169.91519675850506</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>-46.3016817690882,169.91440297374095</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>-46.302062020118285,169.9136570041301</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>-46.302309052940046,169.91281338999346</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>-46.30260980284183,169.91199993839848</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>-46.302923619964076,169.9112219131765</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>-46.30333903428001,169.9105485090086</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-46.29881954289625,169.92336045261115</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-46.29899421177492,169.92249248297927</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-46.29923314975771,169.9216637626502</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-46.299484758414806,169.9208427808193</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-46.29975475267481,169.9200330269253</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-46.30006815592049,169.91924576162825</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-46.30035738275856,169.9184436598302</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-46.30063315897408,169.9176361708166</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>-46.300897545242,169.91682343476242</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>-46.30110705155883,169.9159791496828</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-46.301366701437175,169.91517873940313</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>-46.301653890388735,169.91438581782035</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>-46.30201499093579,169.91362566326222</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>-46.302284710771495,169.91279222660623</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>-46.30258633767499,169.91197567301234</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>-46.30290261277402,169.9112002731844</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>-46.30332041835262,169.91052940611135</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-46.29880695384885,169.92335276465235</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-46.298980628816075,169.9224841882064</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-46.2992221342796,169.92165703588157</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-46.29947722148865,169.9208381783527</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-46.29974721572892,169.92002842451535</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-46.30005895631888,169.91923984264588</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-46.300346551433506,169.9184360361336</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-46.300615430665,169.917623204877</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-46.300884630006216,169.91681398908023</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-46.30109611792343,169.9159715328908</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-46.301350089709544,169.91516812757885</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>-46.30163734516543,169.91437563627306</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>-46.30197237073257,169.9135972606457</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>-46.302268148850985,169.91277782747673</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>-46.30257303343499,169.91196191507663</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>-46.30288936433514,169.91118662567166</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>-46.30330700608816,169.91051564300827</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0526/nzd0526.xlsx
+++ b/data/nzd0526/nzd0526.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S432"/>
+  <dimension ref="A1:S433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27614,6 +27614,69 @@
         <v>303.87</v>
       </c>
       <c r="S432" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>325.67</v>
+      </c>
+      <c r="C433" t="n">
+        <v>316.02</v>
+      </c>
+      <c r="D433" t="n">
+        <v>314.17</v>
+      </c>
+      <c r="E433" t="n">
+        <v>313.96</v>
+      </c>
+      <c r="F433" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="G433" t="n">
+        <v>322.03</v>
+      </c>
+      <c r="H433" t="n">
+        <v>322.96</v>
+      </c>
+      <c r="I433" t="n">
+        <v>318.94</v>
+      </c>
+      <c r="J433" t="n">
+        <v>314.86</v>
+      </c>
+      <c r="K433" t="n">
+        <v>304.82</v>
+      </c>
+      <c r="L433" t="n">
+        <v>302.55</v>
+      </c>
+      <c r="M433" t="n">
+        <v>306.68</v>
+      </c>
+      <c r="N433" t="n">
+        <v>314.19</v>
+      </c>
+      <c r="O433" t="n">
+        <v>314.49</v>
+      </c>
+      <c r="P433" t="n">
+        <v>304.37</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>296.58</v>
+      </c>
+      <c r="R433" t="n">
+        <v>302.64</v>
+      </c>
+      <c r="S433" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27630,7 +27693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B445"/>
+  <dimension ref="A1:B446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32083,6 +32146,16 @@
       </c>
       <c r="B445" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>-0.27</v>
       </c>
     </row>
   </sheetData>
@@ -32251,28 +32324,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.030999425159676</v>
+        <v>3.995950464304962</v>
       </c>
       <c r="J2" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K2" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5158025585940375</v>
+        <v>0.5088797503774182</v>
       </c>
       <c r="M2" t="n">
-        <v>24.62010386739638</v>
+        <v>24.74599969627386</v>
       </c>
       <c r="N2" t="n">
-        <v>885.4296643030465</v>
+        <v>897.1199907843351</v>
       </c>
       <c r="O2" t="n">
-        <v>29.75617018877004</v>
+        <v>29.95196138459609</v>
       </c>
       <c r="P2" t="n">
-        <v>294.316194372084</v>
+        <v>294.6826943530928</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32329,28 +32402,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.276773364571302</v>
+        <v>4.238700484948709</v>
       </c>
       <c r="J3" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K3" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5718784666547765</v>
+        <v>0.5638062632504218</v>
       </c>
       <c r="M3" t="n">
-        <v>23.15456150417573</v>
+        <v>23.29992801771731</v>
       </c>
       <c r="N3" t="n">
-        <v>789.8015260165615</v>
+        <v>804.0514070601379</v>
       </c>
       <c r="O3" t="n">
-        <v>28.10340772960748</v>
+        <v>28.35580023663832</v>
       </c>
       <c r="P3" t="n">
-        <v>284.1886573350318</v>
+        <v>284.589159498408</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32407,28 +32480,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.013265874946295</v>
+        <v>3.976996397068913</v>
       </c>
       <c r="J4" t="n">
+        <v>432</v>
+      </c>
+      <c r="K4" t="n">
         <v>431</v>
       </c>
-      <c r="K4" t="n">
-        <v>430</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.562254591107249</v>
+        <v>0.5541042695156652</v>
       </c>
       <c r="M4" t="n">
-        <v>22.09816877985745</v>
+        <v>22.23875450140742</v>
       </c>
       <c r="N4" t="n">
-        <v>728.8961056903653</v>
+        <v>741.9536731562711</v>
       </c>
       <c r="O4" t="n">
-        <v>26.998075962749</v>
+        <v>27.23882657451071</v>
       </c>
       <c r="P4" t="n">
-        <v>285.9871480788345</v>
+        <v>286.3663884217363</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32485,28 +32558,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.015370473854227</v>
+        <v>3.979016599683005</v>
       </c>
       <c r="J5" t="n">
+        <v>432</v>
+      </c>
+      <c r="K5" t="n">
         <v>431</v>
       </c>
-      <c r="K5" t="n">
-        <v>430</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.564410181546783</v>
+        <v>0.556199179295183</v>
       </c>
       <c r="M5" t="n">
-        <v>21.77486087323249</v>
+        <v>21.90919970175537</v>
       </c>
       <c r="N5" t="n">
-        <v>723.2947264231965</v>
+        <v>736.4340083689185</v>
       </c>
       <c r="O5" t="n">
-        <v>26.89413925789774</v>
+        <v>27.13731763400573</v>
       </c>
       <c r="P5" t="n">
-        <v>285.9150856979566</v>
+        <v>286.2952085040557</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32563,28 +32636,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.319104325117025</v>
+        <v>4.28123080237617</v>
       </c>
       <c r="J6" t="n">
+        <v>432</v>
+      </c>
+      <c r="K6" t="n">
         <v>431</v>
       </c>
-      <c r="K6" t="n">
-        <v>430</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.6013535976873292</v>
+        <v>0.5930292142385276</v>
       </c>
       <c r="M6" t="n">
-        <v>21.43746302207088</v>
+        <v>21.58341539392245</v>
       </c>
       <c r="N6" t="n">
-        <v>718.8305065377768</v>
+        <v>733.2448237067567</v>
       </c>
       <c r="O6" t="n">
-        <v>26.81101464953866</v>
+        <v>27.07849374885458</v>
       </c>
       <c r="P6" t="n">
-        <v>282.6672828263303</v>
+        <v>283.0632953578506</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32641,28 +32714,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.074098775176073</v>
+        <v>4.037647305339216</v>
       </c>
       <c r="J7" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K7" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5980799756803593</v>
+        <v>0.5895106237214249</v>
       </c>
       <c r="M7" t="n">
-        <v>20.41217881807666</v>
+        <v>20.53829820405812</v>
       </c>
       <c r="N7" t="n">
-        <v>647.4900329644024</v>
+        <v>660.8527730180317</v>
       </c>
       <c r="O7" t="n">
-        <v>25.44582545260425</v>
+        <v>25.707056871957</v>
       </c>
       <c r="P7" t="n">
-        <v>292.6094371318565</v>
+        <v>292.9906028690755</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32719,28 +32792,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.279183435648376</v>
+        <v>4.242322923592374</v>
       </c>
       <c r="J8" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K8" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6132373172035959</v>
+        <v>0.6049935029022451</v>
       </c>
       <c r="M8" t="n">
-        <v>20.81712446607542</v>
+        <v>20.94546703954228</v>
       </c>
       <c r="N8" t="n">
-        <v>673.0460133017594</v>
+        <v>686.7639064298645</v>
       </c>
       <c r="O8" t="n">
-        <v>25.94313036820652</v>
+        <v>26.20618069139157</v>
       </c>
       <c r="P8" t="n">
-        <v>288.9574898849337</v>
+        <v>289.3424705341595</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32797,28 +32870,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.370759324613596</v>
+        <v>4.332738674789164</v>
       </c>
       <c r="J9" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K9" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6216183252457748</v>
+        <v>0.6131010514225832</v>
       </c>
       <c r="M9" t="n">
-        <v>20.74317687279886</v>
+        <v>20.88666970025902</v>
       </c>
       <c r="N9" t="n">
-        <v>677.6836864607577</v>
+        <v>692.3679670202281</v>
       </c>
       <c r="O9" t="n">
-        <v>26.03235844983619</v>
+        <v>26.3128859500479</v>
       </c>
       <c r="P9" t="n">
-        <v>285.0263688023458</v>
+        <v>285.423466228208</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32875,28 +32948,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.250397125021156</v>
+        <v>4.213487336459085</v>
       </c>
       <c r="J10" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K10" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5851859857539687</v>
+        <v>0.5772638758334456</v>
       </c>
       <c r="M10" t="n">
-        <v>21.95959149211571</v>
+        <v>22.09037659089085</v>
       </c>
       <c r="N10" t="n">
-        <v>740.8111314635746</v>
+        <v>754.2443489511259</v>
       </c>
       <c r="O10" t="n">
-        <v>27.21784582702266</v>
+        <v>27.46350940705004</v>
       </c>
       <c r="P10" t="n">
-        <v>281.2112193137169</v>
+        <v>281.5988496392589</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32953,28 +33026,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3.939862260153937</v>
+        <v>3.904667126379734</v>
       </c>
       <c r="J11" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K11" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5784658283635826</v>
+        <v>0.5702415785673152</v>
       </c>
       <c r="M11" t="n">
-        <v>20.71492996834545</v>
+        <v>20.82634883621614</v>
       </c>
       <c r="N11" t="n">
-        <v>654.3440127649852</v>
+        <v>666.6029731978899</v>
       </c>
       <c r="O11" t="n">
-        <v>25.58014880263571</v>
+        <v>25.81865552653526</v>
       </c>
       <c r="P11" t="n">
-        <v>275.7811247174223</v>
+        <v>276.1507475652868</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33031,28 +33104,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.076790597162439</v>
+        <v>4.041681792688022</v>
       </c>
       <c r="J12" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K12" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L12" t="n">
-        <v>0.612353765325118</v>
+        <v>0.6041423325436821</v>
       </c>
       <c r="M12" t="n">
-        <v>19.75291570049047</v>
+        <v>19.87971942555734</v>
       </c>
       <c r="N12" t="n">
-        <v>609.7833976471767</v>
+        <v>622.113874855211</v>
       </c>
       <c r="O12" t="n">
-        <v>24.69379269466674</v>
+        <v>24.94221070505201</v>
       </c>
       <c r="P12" t="n">
-        <v>269.6472696848558</v>
+        <v>270.0158025285876</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33109,28 +33182,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>3.874104726184711</v>
+        <v>3.839547565742922</v>
       </c>
       <c r="J13" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K13" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5936260509284818</v>
+        <v>0.5851589118371234</v>
       </c>
       <c r="M13" t="n">
-        <v>19.69170298105097</v>
+        <v>19.80189621532127</v>
       </c>
       <c r="N13" t="n">
-        <v>597.5396237219653</v>
+        <v>609.5515751270497</v>
       </c>
       <c r="O13" t="n">
-        <v>24.44462361587851</v>
+        <v>24.68909830526522</v>
       </c>
       <c r="P13" t="n">
-        <v>278.1848455136912</v>
+        <v>278.5471684364931</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33187,28 +33260,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3.723364946174508</v>
+        <v>3.69139607943083</v>
       </c>
       <c r="J14" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K14" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5868869704960433</v>
+        <v>0.5790728304626974</v>
       </c>
       <c r="M14" t="n">
-        <v>19.16305842913541</v>
+        <v>19.27631389037296</v>
       </c>
       <c r="N14" t="n">
-        <v>567.7205796168391</v>
+        <v>577.8823193298779</v>
       </c>
       <c r="O14" t="n">
-        <v>23.8268877450841</v>
+        <v>24.03918300046567</v>
       </c>
       <c r="P14" t="n">
-        <v>284.2604438010642</v>
+        <v>284.5951110585077</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33265,28 +33338,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>2.876523549431252</v>
+        <v>2.846840511611108</v>
       </c>
       <c r="J15" t="n">
+        <v>432</v>
+      </c>
+      <c r="K15" t="n">
         <v>431</v>
       </c>
-      <c r="K15" t="n">
-        <v>430</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.5074523485708524</v>
+        <v>0.4983170721444712</v>
       </c>
       <c r="M15" t="n">
-        <v>17.19789617098779</v>
+        <v>17.30045269961187</v>
       </c>
       <c r="N15" t="n">
-        <v>466.3803549485443</v>
+        <v>475.1655510001711</v>
       </c>
       <c r="O15" t="n">
-        <v>21.59584114936356</v>
+        <v>21.79829238725298</v>
       </c>
       <c r="P15" t="n">
-        <v>302.3916827173972</v>
+        <v>302.702283031958</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33343,28 +33416,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.705770902662558</v>
+        <v>2.676634569228284</v>
       </c>
       <c r="J16" t="n">
+        <v>432</v>
+      </c>
+      <c r="K16" t="n">
         <v>431</v>
       </c>
-      <c r="K16" t="n">
-        <v>430</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.4571447501132575</v>
+        <v>0.44843185547088</v>
       </c>
       <c r="M16" t="n">
-        <v>17.9898995608017</v>
+        <v>18.10120549442062</v>
       </c>
       <c r="N16" t="n">
-        <v>504.8516093082442</v>
+        <v>513.1874193717672</v>
       </c>
       <c r="O16" t="n">
-        <v>22.46890316210928</v>
+        <v>22.65364031169753</v>
       </c>
       <c r="P16" t="n">
-        <v>295.6720936584995</v>
+        <v>295.9769733134954</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33421,28 +33494,28 @@
         <v>0.1976</v>
       </c>
       <c r="I17" t="n">
-        <v>2.466242153672035</v>
+        <v>2.438165217175235</v>
       </c>
       <c r="J17" t="n">
+        <v>432</v>
+      </c>
+      <c r="K17" t="n">
         <v>431</v>
       </c>
-      <c r="K17" t="n">
-        <v>430</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.4046134987745846</v>
+        <v>0.3963076450924452</v>
       </c>
       <c r="M17" t="n">
-        <v>18.3755858278473</v>
+        <v>18.48946986903724</v>
       </c>
       <c r="N17" t="n">
-        <v>519.7343783022806</v>
+        <v>527.3568659684246</v>
       </c>
       <c r="O17" t="n">
-        <v>22.79768361703181</v>
+        <v>22.96425191397326</v>
       </c>
       <c r="P17" t="n">
-        <v>292.0048213000433</v>
+        <v>292.2986155323132</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33499,28 +33572,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2.046105370370852</v>
+        <v>2.021693630064314</v>
       </c>
       <c r="J18" t="n">
+        <v>432</v>
+      </c>
+      <c r="K18" t="n">
         <v>431</v>
       </c>
-      <c r="K18" t="n">
-        <v>430</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.3587841221756822</v>
+        <v>0.3509781254433399</v>
       </c>
       <c r="M18" t="n">
-        <v>16.78508979809314</v>
+        <v>16.87873253969294</v>
       </c>
       <c r="N18" t="n">
-        <v>434.4886522118655</v>
+        <v>440.1544390012675</v>
       </c>
       <c r="O18" t="n">
-        <v>20.84439138501927</v>
+        <v>20.97985793567887</v>
       </c>
       <c r="P18" t="n">
-        <v>301.3071854306191</v>
+        <v>301.5626274195466</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33558,7 +33631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S432"/>
+  <dimension ref="A1:S433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75341,6 +75414,103 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-46.29880372376424,169.92335079208453</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-46.298980628816075,169.9224841882064</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-46.2992221342796,169.92165703588157</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-46.29947722148865,169.9208381783527</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-46.29974721572892,169.92002842451535</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-46.30005895631888,169.91923984264588</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-46.300346874756656,169.9184362637066</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-46.30061069776778,169.9176197433832</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-46.3008729982715,169.91680548210306</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-46.30108477933809,169.91596363399847</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-46.301335287179235,169.9151586715031</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>-46.30162601168703,169.91436866191657</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>-46.3019493460225,169.91358191672126</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>-46.30225343570163,169.9127650356991</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>-46.30256389590662,169.9119524659488</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>-46.30288116640537,169.91117818080517</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>-46.30329799128662,169.91050639240174</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0526/nzd0526.xlsx
+++ b/data/nzd0526/nzd0526.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S433"/>
+  <dimension ref="A1:S435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27679,6 +27679,132 @@
       <c r="S433" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>325.02</v>
+      </c>
+      <c r="C434" t="n">
+        <v>315.15</v>
+      </c>
+      <c r="D434" t="n">
+        <v>313.47</v>
+      </c>
+      <c r="E434" t="n">
+        <v>313.21</v>
+      </c>
+      <c r="F434" t="n">
+        <v>314.87</v>
+      </c>
+      <c r="G434" t="n">
+        <v>321.45</v>
+      </c>
+      <c r="H434" t="n">
+        <v>322.36</v>
+      </c>
+      <c r="I434" t="n">
+        <v>317.94</v>
+      </c>
+      <c r="J434" t="n">
+        <v>313.92</v>
+      </c>
+      <c r="K434" t="n">
+        <v>303.87</v>
+      </c>
+      <c r="L434" t="n">
+        <v>301.52</v>
+      </c>
+      <c r="M434" t="n">
+        <v>306.05</v>
+      </c>
+      <c r="N434" t="n">
+        <v>313.48</v>
+      </c>
+      <c r="O434" t="n">
+        <v>313.83</v>
+      </c>
+      <c r="P434" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>295.83</v>
+      </c>
+      <c r="R434" t="n">
+        <v>301.57</v>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>324.44</v>
+      </c>
+      <c r="C435" t="n">
+        <v>313.17</v>
+      </c>
+      <c r="D435" t="n">
+        <v>312.08</v>
+      </c>
+      <c r="E435" t="n">
+        <v>312.33</v>
+      </c>
+      <c r="F435" t="n">
+        <v>313.73</v>
+      </c>
+      <c r="G435" t="n">
+        <v>319.91</v>
+      </c>
+      <c r="H435" t="n">
+        <v>321.11</v>
+      </c>
+      <c r="I435" t="n">
+        <v>316.57</v>
+      </c>
+      <c r="J435" t="n">
+        <v>312.48</v>
+      </c>
+      <c r="K435" t="n">
+        <v>301.88</v>
+      </c>
+      <c r="L435" t="n">
+        <v>300.02</v>
+      </c>
+      <c r="M435" t="n">
+        <v>304.75</v>
+      </c>
+      <c r="N435" t="n">
+        <v>311.66</v>
+      </c>
+      <c r="O435" t="n">
+        <v>311.91</v>
+      </c>
+      <c r="P435" t="n">
+        <v>302.57</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>294.21</v>
+      </c>
+      <c r="R435" t="n">
+        <v>300.05</v>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27693,7 +27819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B446"/>
+  <dimension ref="A1:B448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32156,6 +32282,26 @@
       </c>
       <c r="B446" t="n">
         <v>-0.27</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -32324,28 +32470,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>3.995950464304962</v>
+        <v>3.925503459428143</v>
       </c>
       <c r="J2" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K2" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5088797503774182</v>
+        <v>0.4949540055215254</v>
       </c>
       <c r="M2" t="n">
-        <v>24.74599969627386</v>
+        <v>24.99980463790792</v>
       </c>
       <c r="N2" t="n">
-        <v>897.1199907843351</v>
+        <v>920.7006848865116</v>
       </c>
       <c r="O2" t="n">
-        <v>29.95196138459609</v>
+        <v>30.34305002610172</v>
       </c>
       <c r="P2" t="n">
-        <v>294.6826943530928</v>
+        <v>295.4228146854992</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32402,28 +32548,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.238700484948709</v>
+        <v>4.161418225075602</v>
       </c>
       <c r="J3" t="n">
+        <v>434</v>
+      </c>
+      <c r="K3" t="n">
         <v>432</v>
       </c>
-      <c r="K3" t="n">
-        <v>430</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.5638062632504218</v>
+        <v>0.5472953482392949</v>
       </c>
       <c r="M3" t="n">
-        <v>23.29992801771731</v>
+        <v>23.59231061172072</v>
       </c>
       <c r="N3" t="n">
-        <v>804.0514070601379</v>
+        <v>833.4244312760608</v>
       </c>
       <c r="O3" t="n">
-        <v>28.35580023663832</v>
+        <v>28.86909127901432</v>
       </c>
       <c r="P3" t="n">
-        <v>284.589159498408</v>
+        <v>285.4059442519396</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32480,28 +32626,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>3.976996397068913</v>
+        <v>3.903736825292069</v>
       </c>
       <c r="J4" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K4" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5541042695156652</v>
+        <v>0.5375856096853989</v>
       </c>
       <c r="M4" t="n">
-        <v>22.23875450140742</v>
+        <v>22.51978201119514</v>
       </c>
       <c r="N4" t="n">
-        <v>741.9536731562711</v>
+        <v>768.5710835908357</v>
       </c>
       <c r="O4" t="n">
-        <v>27.23882657451071</v>
+        <v>27.72311460840639</v>
       </c>
       <c r="P4" t="n">
-        <v>286.3663884217363</v>
+        <v>287.1360284117754</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32558,28 +32704,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3.979016599683005</v>
+        <v>3.90576656318642</v>
       </c>
       <c r="J5" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K5" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L5" t="n">
-        <v>0.556199179295183</v>
+        <v>0.5396297527385945</v>
       </c>
       <c r="M5" t="n">
-        <v>21.90919970175537</v>
+        <v>22.18030473349511</v>
       </c>
       <c r="N5" t="n">
-        <v>736.4340083689185</v>
+        <v>763.0679265569918</v>
       </c>
       <c r="O5" t="n">
-        <v>27.13731763400573</v>
+        <v>27.62368415973857</v>
       </c>
       <c r="P5" t="n">
-        <v>286.2952085040557</v>
+        <v>287.0647459260479</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32636,28 +32782,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.28123080237617</v>
+        <v>4.204894587077296</v>
       </c>
       <c r="J6" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K6" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5930292142385276</v>
+        <v>0.5762055050291939</v>
       </c>
       <c r="M6" t="n">
-        <v>21.58341539392245</v>
+        <v>21.87918796012662</v>
       </c>
       <c r="N6" t="n">
-        <v>733.2448237067567</v>
+        <v>762.4781542139966</v>
       </c>
       <c r="O6" t="n">
-        <v>27.07849374885458</v>
+        <v>27.61300697522812</v>
       </c>
       <c r="P6" t="n">
-        <v>283.0632953578506</v>
+        <v>283.8652560600944</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32714,28 +32860,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.037647305339216</v>
+        <v>3.964057704923464</v>
       </c>
       <c r="J7" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K7" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5895106237214249</v>
+        <v>0.5721510718339149</v>
       </c>
       <c r="M7" t="n">
-        <v>20.53829820405812</v>
+        <v>20.794073753244</v>
       </c>
       <c r="N7" t="n">
-        <v>660.8527730180317</v>
+        <v>688.0520890762309</v>
       </c>
       <c r="O7" t="n">
-        <v>25.707056871957</v>
+        <v>26.23074701712155</v>
       </c>
       <c r="P7" t="n">
-        <v>292.9906028690755</v>
+        <v>293.7637438573696</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32792,28 +32938,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.242322923592374</v>
+        <v>4.16801471767687</v>
       </c>
       <c r="J8" t="n">
+        <v>434</v>
+      </c>
+      <c r="K8" t="n">
         <v>432</v>
       </c>
-      <c r="K8" t="n">
-        <v>430</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.6049935029022451</v>
+        <v>0.5883187776167227</v>
       </c>
       <c r="M8" t="n">
-        <v>20.94546703954228</v>
+        <v>21.20479411374744</v>
       </c>
       <c r="N8" t="n">
-        <v>686.7639064298645</v>
+        <v>714.5954681722488</v>
       </c>
       <c r="O8" t="n">
-        <v>26.20618069139157</v>
+        <v>26.73191852771231</v>
       </c>
       <c r="P8" t="n">
-        <v>289.3424705341595</v>
+        <v>290.1222511550219</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32870,28 +33016,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.332738674789164</v>
+        <v>4.255715840032617</v>
       </c>
       <c r="J9" t="n">
+        <v>434</v>
+      </c>
+      <c r="K9" t="n">
         <v>432</v>
       </c>
-      <c r="K9" t="n">
-        <v>430</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.6131010514225832</v>
+        <v>0.5957268475210912</v>
       </c>
       <c r="M9" t="n">
-        <v>20.88666970025902</v>
+        <v>21.18216275695513</v>
       </c>
       <c r="N9" t="n">
-        <v>692.3679670202281</v>
+        <v>722.4809389136951</v>
       </c>
       <c r="O9" t="n">
-        <v>26.3128859500479</v>
+        <v>26.87900554175499</v>
       </c>
       <c r="P9" t="n">
-        <v>285.423466228208</v>
+        <v>286.231734113112</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32948,28 +33094,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.213487336459085</v>
+        <v>4.13868087729926</v>
       </c>
       <c r="J10" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K10" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5772638758334456</v>
+        <v>0.5610911016407323</v>
       </c>
       <c r="M10" t="n">
-        <v>22.09037659089085</v>
+        <v>22.36200140033965</v>
       </c>
       <c r="N10" t="n">
-        <v>754.2443489511259</v>
+        <v>781.8367794893801</v>
       </c>
       <c r="O10" t="n">
-        <v>27.46350940705004</v>
+        <v>27.96134437914923</v>
       </c>
       <c r="P10" t="n">
-        <v>281.5988496392589</v>
+        <v>282.3881829737239</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33026,28 +33172,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3.904667126379734</v>
+        <v>3.833019275772152</v>
       </c>
       <c r="J11" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K11" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5702415785673152</v>
+        <v>0.5533347405431545</v>
       </c>
       <c r="M11" t="n">
-        <v>20.82634883621614</v>
+        <v>21.05095287792219</v>
       </c>
       <c r="N11" t="n">
-        <v>666.6029731978899</v>
+        <v>692.0340376575296</v>
       </c>
       <c r="O11" t="n">
-        <v>25.81865552653526</v>
+        <v>26.30653982677178</v>
       </c>
       <c r="P11" t="n">
-        <v>276.1507475652868</v>
+        <v>276.9067551856269</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33104,28 +33250,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.041681792688022</v>
+        <v>3.970344501480825</v>
       </c>
       <c r="J12" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K12" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6041423325436821</v>
+        <v>0.5872973788604284</v>
       </c>
       <c r="M12" t="n">
-        <v>19.87971942555734</v>
+        <v>20.14521073334172</v>
       </c>
       <c r="N12" t="n">
-        <v>622.113874855211</v>
+        <v>647.5749028803828</v>
       </c>
       <c r="O12" t="n">
-        <v>24.94221070505201</v>
+        <v>25.44749305688839</v>
       </c>
       <c r="P12" t="n">
-        <v>270.0158025285876</v>
+        <v>270.7681699487852</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33182,28 +33328,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>3.839547565742922</v>
+        <v>3.7697731977338</v>
       </c>
       <c r="J13" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K13" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5851589118371234</v>
+        <v>0.5680030284976338</v>
       </c>
       <c r="M13" t="n">
-        <v>19.80189621532127</v>
+        <v>20.0227631604703</v>
       </c>
       <c r="N13" t="n">
-        <v>609.5515751270497</v>
+        <v>634.0065435520813</v>
       </c>
       <c r="O13" t="n">
-        <v>24.68909830526522</v>
+        <v>25.17948656251913</v>
       </c>
       <c r="P13" t="n">
-        <v>278.5471684364931</v>
+        <v>279.2822229103825</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33260,28 +33406,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3.69139607943083</v>
+        <v>3.626438303769924</v>
       </c>
       <c r="J14" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K14" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5790728304626974</v>
+        <v>0.5630447859598742</v>
       </c>
       <c r="M14" t="n">
-        <v>19.27631389037296</v>
+        <v>19.50388485354278</v>
       </c>
       <c r="N14" t="n">
-        <v>577.8823193298779</v>
+        <v>598.8770428742938</v>
       </c>
       <c r="O14" t="n">
-        <v>24.03918300046567</v>
+        <v>24.47196442614066</v>
       </c>
       <c r="P14" t="n">
-        <v>284.5951110585077</v>
+        <v>285.2783601953346</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33338,28 +33484,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>2.846840511611108</v>
+        <v>2.78648558585719</v>
       </c>
       <c r="J15" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K15" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4983170721444712</v>
+        <v>0.479677020035125</v>
       </c>
       <c r="M15" t="n">
-        <v>17.30045269961187</v>
+        <v>17.50748685603457</v>
       </c>
       <c r="N15" t="n">
-        <v>475.1655510001711</v>
+        <v>493.3421043637709</v>
       </c>
       <c r="O15" t="n">
-        <v>21.79829238725298</v>
+        <v>22.21130577799898</v>
       </c>
       <c r="P15" t="n">
-        <v>302.702283031958</v>
+        <v>303.3368199655542</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33416,28 +33562,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.676634569228284</v>
+        <v>2.617740791594932</v>
       </c>
       <c r="J16" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K16" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L16" t="n">
-        <v>0.44843185547088</v>
+        <v>0.430858520435905</v>
       </c>
       <c r="M16" t="n">
-        <v>18.10120549442062</v>
+        <v>18.32538376228097</v>
       </c>
       <c r="N16" t="n">
-        <v>513.1874193717672</v>
+        <v>530.2117165477994</v>
       </c>
       <c r="O16" t="n">
-        <v>22.65364031169753</v>
+        <v>23.02632659691509</v>
       </c>
       <c r="P16" t="n">
-        <v>295.9769733134954</v>
+        <v>296.5961453184489</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33494,28 +33640,28 @@
         <v>0.1976</v>
       </c>
       <c r="I17" t="n">
-        <v>2.438165217175235</v>
+        <v>2.381071139899108</v>
       </c>
       <c r="J17" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K17" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3963076450924452</v>
+        <v>0.3794271233970007</v>
       </c>
       <c r="M17" t="n">
-        <v>18.48946986903724</v>
+        <v>18.72955777716206</v>
       </c>
       <c r="N17" t="n">
-        <v>527.3568659684246</v>
+        <v>543.1498269749633</v>
       </c>
       <c r="O17" t="n">
-        <v>22.96425191397326</v>
+        <v>23.30557501918722</v>
       </c>
       <c r="P17" t="n">
-        <v>292.2986155323132</v>
+        <v>292.898868816992</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33572,28 +33718,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2.021693630064314</v>
+        <v>1.971639715624738</v>
       </c>
       <c r="J18" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K18" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3509781254433399</v>
+        <v>0.334936936082747</v>
       </c>
       <c r="M18" t="n">
-        <v>16.87873253969294</v>
+        <v>17.07186364188355</v>
       </c>
       <c r="N18" t="n">
-        <v>440.1544390012675</v>
+        <v>452.1321478695131</v>
       </c>
       <c r="O18" t="n">
-        <v>20.97985793567887</v>
+        <v>21.26339925481138</v>
       </c>
       <c r="P18" t="n">
-        <v>301.5626274195466</v>
+        <v>302.088865079547</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33631,7 +33777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S433"/>
+  <dimension ref="A1:S435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75511,6 +75657,200 @@
         </is>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-46.298798340289835,169.92334750447196</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-46.29897342322184,169.92247978793213</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-46.29921633665941,169.92165349547807</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-46.2994710097362,169.92083438511196</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-46.2997415837253,169.92002498535268</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-46.30005419223937,169.91923677745933</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-46.30034202490947,169.91843285011203</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-46.30060267590789,169.91761387644587</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-46.30086545769837,169.91679996723698</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>-46.30107708529777,169.91595827403762</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-46.30132681684212,169.9151532605286</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>-46.30162079994133,169.9143654547317</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>-46.30194354902074,169.91357805353655</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>-46.30224835157641,169.91276061550522</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>-46.3025593636923,169.91194777918255</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>-46.30287567671992,169.91117252576205</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>-46.30329014914162,169.9104983451286</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-46.298793536574145,169.92334457091053</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-46.29895702428267,169.92246977351908</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-46.29920482424188,169.92164646525038</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-46.29946372127984,169.92082993437717</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-46.29973214183666,169.92001921969916</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>-46.30004154278652,169.91922863886307</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-46.300331921060874,169.91842573845855</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-46.30059168595938,169.91760583874444</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>-46.300853906181594,169.91679151893436</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>-46.301060968307304,169.9159470463349</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-46.301314481399345,169.91514538047159</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>-46.30161004554524,169.914358836733</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>-46.301928689100194,169.91356815072876</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>-46.302233561393095,169.91274775676405</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>-46.302550737864536,169.91193885921015</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>-46.3028638189985,169.91116031087267</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>-46.30327900889735,169.91048691349212</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
